--- a/M025_FINAL_PACKAGE/M025_tables_and_summary.xlsx
+++ b/M025_FINAL_PACKAGE/M025_tables_and_summary.xlsx
@@ -20,7 +20,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subgroup_Histology_x_TR" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subgroup_NumExams" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity_Arms" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Gates" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity_Era_Patient" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity_Era_Nodule" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity_Match_Window" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Gates" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 2026-05-05T04:39:20.042644+00:00. Manuscript headline = patient-level. Nodule-level = sister analysis.</t>
+          <t>Built 2026-05-05T05:08:53.125637+00:00. Manuscript headline = patient-level. Nodule-level = sister analysis.</t>
         </is>
       </c>
     </row>
@@ -571,7 +574,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-05T04:39:20.042644+00:00</t>
+          <t>2026-05-05T05:08:53.125637+00:00</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1634,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1648,7 +1651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Locked from cursor 1d4ecc1 and Cowork pre-bake; verify before manuscript inclusion.</t>
+          <t>Locked from cursor 1d4ecc1 and Cowork pre-bake + mig_307c sensitivity arms.</t>
         </is>
       </c>
     </row>
@@ -1739,10 +1742,58 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>S2 era split (patient grain)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Pre-2017 n=422 ROM 40.0%; Post-2017 n=2,953 ROM 44.4%; per-TR ROM directionally similar (see Sensitivity_Era_Patient sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>S2 era split (nodule strict)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Pre-2017 n=381 ROM 25.2%; Post-2017 n=3,306 ROM 16.2%; post-2017-only TR4 18.0% / TR5 24.4% (both in ACR bands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>S3 tighter US-to-surgery window (nodule strict)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>180d: TR4 15.7% / TR5 22.2% (still in ACR bands); 90d: TR4 11.3% / TR5 16.8%; 30d: tight bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Provenance check (strict subset)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>99.3% inm_v1 structured source (Script 246); 0.7% LLM-augmented; institutional independent verification of feature extractions</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>ACR FNA compliance flagged</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>1,553 unnecessary FNAs by ACR criteria; 472 cancers below ACR FNA threshold</t>
         </is>
@@ -1754,6 +1805,1089 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity S2 — Patient cohort split by ACR-2017 era</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Era boundary = surg_first_date &lt; 2017-05-01 (ACR TI-RADS 2017 publication date).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>era</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>tr_category</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>n_malignant</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>rom_pct</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>tp_thr3</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>fp_thr3</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>tp_thr4</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>fp_thr4</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>tp_thr5</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>fp_thr5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>TR1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TR2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TR3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>740</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>533</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TR4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>440</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>212</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>212</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>212</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TR5</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>58.08</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>534</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>534</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>2953</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1310</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1295</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>952</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>762</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>740</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TR1</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>TR2</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>TR3</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>TR4</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TR5</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n">
+        <v>422</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity S2 — Nodule strict cohort split by ACR-2017 era</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Era boundary = exam_date &lt; 2017-05-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>era</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>tr_category</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>n_malignant</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>rom_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>TR2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TR3</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1388</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TR4</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>771</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>18.03</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TR5</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1116</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>272</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>24.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>post_2017</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n">
+        <v>3306</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>535</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>16.18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TR3</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13.17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TR4</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>24.72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>TR5</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>pre_2017</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity S3 — Tighter US-to-surgery match-window (nodule strict)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Recomputes ROM at 365 / 180 / 90 / 30 day windows. Median US-to-malignant-surgery interval ~60–80 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>tr_category</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>m_w365</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w365_pct</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>m_w180</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w180_pct</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>m_w90</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w90_pct</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>m_w30</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w30_pct</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>median_days_to_surg_malig</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>q75_days_to_surg_malig</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>q95_days_to_surg_malig</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>TR2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TR3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1555</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TR4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>TR5</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1241</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>324</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/M025_FINAL_PACKAGE/M025_tables_and_summary.xlsx
+++ b/M025_FINAL_PACKAGE/M025_tables_and_summary.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 2026-05-05T05:08:53.125637+00:00. Manuscript headline = patient-level. Nodule-level = sister analysis.</t>
+          <t>Built 2026-05-05T05:18:12.241134+00:00. Manuscript headline = patient-level. Nodule-level = sister analysis.</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-05T05:08:53.125637+00:00</t>
+          <t>2026-05-05T05:18:12.241134+00:00</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mig_307 (manuscript closeout) + mig_307b (analytic spine refresh)</t>
+          <t>mig_307b (analytic spine) + mig_307c (sensitivity tables) + mig_307d (sensitivity publication outputs)</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Locked from cursor 1d4ecc1 and Cowork pre-bake + mig_307c sensitivity arms.</t>
+          <t>mig_307c sensitivity tables; mig_307d adds Wilson 95% CIs, diagnostics CSVs, and figures under 06_figures_sensitivity/.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1824,6 +1824,8 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1836,7 +1838,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Era boundary = surg_first_date &lt; 2017-05-01 (ACR TI-RADS 2017 publication date).</t>
+          <t>Era boundary = surg_first_date &lt; 2017-05-01 (ACR TI-RADS 2017 publication date). lo_95 / hi_95 = Wilson 95% CI for ROM (n_malignant / n_total).</t>
         </is>
       </c>
     </row>
@@ -1896,6 +1898,16 @@
           <t>fp_thr5</t>
         </is>
       </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>lo_95</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>hi_95</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1935,6 +1947,12 @@
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="6" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>34.82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1974,6 +1992,12 @@
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="6" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>37.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2013,6 +2037,12 @@
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L7" s="6" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>31.31</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2052,6 +2082,12 @@
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L8" s="6" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>52.85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2090,6 +2126,12 @@
       </c>
       <c r="K9" s="6" t="n">
         <v>534</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>60.77</v>
       </c>
     </row>
     <row r="10">
@@ -2126,6 +2168,12 @@
       <c r="K10" s="6" t="n">
         <v>534</v>
       </c>
+      <c r="L10" s="6" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>46.16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2165,6 +2213,12 @@
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L11" s="6" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>35.96</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2204,6 +2258,12 @@
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L12" s="6" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>45.38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2243,6 +2303,12 @@
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L13" s="6" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>33.81</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2282,6 +2348,12 @@
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="L14" s="6" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>53.93</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2320,6 +2392,12 @@
       </c>
       <c r="K15" s="6" t="n">
         <v>44</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>72.62</v>
       </c>
     </row>
     <row r="16">
@@ -2355,6 +2433,12 @@
       </c>
       <c r="K16" s="6" t="n">
         <v>44</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>44.79</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2376,6 +2460,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2388,7 +2474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Era boundary = exam_date &lt; 2017-05-01.</t>
+          <t>Era boundary = exam_date &lt; 2017-05-01. lo_95 / hi_95 = Wilson CI for ROM.</t>
         </is>
       </c>
     </row>
@@ -2418,6 +2504,16 @@
           <t>rom_pct</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>lo_95</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>hi_95</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2439,6 +2535,12 @@
       <c r="E5" s="6" t="n">
         <v>12.9</v>
       </c>
+      <c r="F5" s="6" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>28.85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2460,6 +2562,12 @@
       <c r="E6" s="6" t="n">
         <v>8.65</v>
       </c>
+      <c r="F6" s="6" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>10.24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2481,6 +2589,12 @@
       <c r="E7" s="6" t="n">
         <v>18.03</v>
       </c>
+      <c r="F7" s="6" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2501,6 +2615,12 @@
       </c>
       <c r="E8" s="6" t="n">
         <v>24.37</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>26.98</v>
       </c>
     </row>
     <row r="9">
@@ -2519,6 +2639,12 @@
       <c r="E9" s="6" t="n">
         <v>16.18</v>
       </c>
+      <c r="F9" s="6" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>17.48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2540,6 +2666,12 @@
       <c r="E10" s="6" t="n">
         <v>13.17</v>
       </c>
+      <c r="F10" s="6" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>19.14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2561,6 +2693,12 @@
       <c r="E11" s="6" t="n">
         <v>24.72</v>
       </c>
+      <c r="F11" s="6" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>34.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2581,6 +2719,12 @@
       </c>
       <c r="E12" s="6" t="n">
         <v>41.6</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>50.37</v>
       </c>
     </row>
     <row r="13">
@@ -2598,6 +2742,12 @@
       </c>
       <c r="E13" s="6" t="n">
         <v>25.2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>29.79</v>
       </c>
     </row>
   </sheetData>
@@ -2611,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2627,6 +2777,14 @@
     <col width="27" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2639,7 +2797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Recomputes ROM at 365 / 180 / 90 / 30 day windows. Median US-to-malignant-surgery interval ~60–80 days.</t>
+          <t>ROM at 365 / 180 / 90 / 30 d: Wilson 95% CIs in rom_w*_lo_95 / rom_w*_hi_95 vs n_total.</t>
         </is>
       </c>
     </row>
@@ -2709,6 +2867,46 @@
           <t>q95_days_to_surg_malig</t>
         </is>
       </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w365_lo_95</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w365_hi_95</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w180_lo_95</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w180_hi_95</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w90_lo_95</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w90_hi_95</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w30_lo_95</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>rom_w30_hi_95</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2752,6 +2950,30 @@
       <c r="M5" s="5" t="n">
         <v>56</v>
       </c>
+      <c r="N5" s="6" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>24.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2795,6 +3017,30 @@
       <c r="M6" s="5" t="n">
         <v>288</v>
       </c>
+      <c r="N6" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>2.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2838,6 +3084,30 @@
       <c r="M7" s="5" t="n">
         <v>291</v>
       </c>
+      <c r="N7" s="6" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>7.84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2880,6 +3150,30 @@
       </c>
       <c r="M8" s="5" t="n">
         <v>264</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>10.66</v>
       </c>
     </row>
   </sheetData>
